--- a/resource/groundTruths/decision/CF_M04_ground_truth_decision.xlsx
+++ b/resource/groundTruths/decision/CF_M04_ground_truth_decision.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/oguzarslan/Desktop/upc/semester-4/Thesis/MappingGenerator/resource/groundTruths/decision/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{474D4B29-D0DA-B040-A4ED-757F242A4AE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F447A375-965F-B943-A755-7D9554C013A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7120" yWindow="1040" windowWidth="14480" windowHeight="16560" xr2:uid="{BB3B0AD0-61FB-9141-8733-A27066D72F37}"/>
   </bookViews>
